--- a/StructureDefinition-patient-condition-summary.xlsx
+++ b/StructureDefinition-patient-condition-summary.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T01:56:54+00:00</t>
+    <t>2024-06-05T23:37:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-patient-condition-summary.xlsx
+++ b/StructureDefinition-patient-condition-summary.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T23:37:17+00:00</t>
+    <t>2024-06-06T01:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-patient-condition-summary.xlsx
+++ b/StructureDefinition-patient-condition-summary.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T01:43:40+00:00</t>
+    <t>2024-06-07T05:32:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A FHIR Condition representation of a PatientConditionSummary</t>
+    <t>Summary of Patient Conditions</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -5882,7 +5882,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-patient-condition-summary.xlsx
+++ b/StructureDefinition-patient-condition-summary.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T05:32:15+00:00</t>
+    <t>2024-06-09T05:26:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-patient-condition-summary.xlsx
+++ b/StructureDefinition-patient-condition-summary.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-09T05:26:46+00:00</t>
+    <t>2024-06-10T02:42:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-patient-condition-summary.xlsx
+++ b/StructureDefinition-patient-condition-summary.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-10T02:42:44+00:00</t>
+    <t>2024-06-10T05:34:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-patient-condition-summary.xlsx
+++ b/StructureDefinition-patient-condition-summary.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-10T05:34:33+00:00</t>
+    <t>2024-06-10T23:00:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-patient-condition-summary.xlsx
+++ b/StructureDefinition-patient-condition-summary.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-10T23:00:50+00:00</t>
+    <t>2024-06-11T04:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-patient-condition-summary.xlsx
+++ b/StructureDefinition-patient-condition-summary.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T04:27:51+00:00</t>
+    <t>2024-06-11T06:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-patient-condition-summary.xlsx
+++ b/StructureDefinition-patient-condition-summary.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://ig.opennz.org/fsh-ig/StructureDefinition/patient-condition-summary</t>
+    <t>http://ig.opennz.org/StructureDefinition/patient-condition-summary</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>PatientConditionSummary</t>
+    <t>AssistanceNeedsProfile</t>
   </si>
   <si>
     <t>Title</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T06:20:54+00:00</t>
+    <t>2024-06-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-patient-condition-summary.xlsx
+++ b/StructureDefinition-patient-condition-summary.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://ig.opennz.org/StructureDefinition/patient-condition-summary</t>
+    <t>https://ig.opennz.org/StructureDefinition/patient-condition-summary</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T09:45:49+00:00</t>
+    <t>2024-06-13T01:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -66,7 +66,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>FHIR New Republic (http://ig.opennz.org)</t>
+    <t>FHIR New Republic (https://ig.opennz.org)</t>
   </si>
   <si>
     <t>Description</t>

--- a/StructureDefinition-patient-condition-summary.xlsx
+++ b/StructureDefinition-patient-condition-summary.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-13T01:01:15+00:00</t>
+    <t>2024-06-13T05:29:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
